--- a/tools/importer/reports/import-help-and-support.report.xlsx
+++ b/tools/importer/reports/import-help-and-support.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="48">
   <si>
     <t>_reportFile</t>
   </si>
@@ -64,19 +64,22 @@
     <t>index.report.json</t>
   </si>
   <si>
-    <t>["carousel-hero","cards-quicklink","cards-quicklink","carousel-fare","cards-news","columns-appbanner","accordion-faq","columns-newsletter"]</t>
+    <t>["hero-support","cards-quicklink","app-promo","carousel-tips","accordion-faq","cards-support"]</t>
   </si>
   <si>
     <t>index</t>
   </si>
   <si>
-    <t>home-landing</t>
-  </si>
-  <si>
-    <t>2026-07-19T09:47:55.705Z</t>
-  </si>
-  <si>
-    <t>https://www.nileair.com/</t>
+    <t>help-and-support</t>
+  </si>
+  <si>
+    <t>2026-09-21T10:07:19.295Z</t>
+  </si>
+  <si>
+    <t>TAQA Distribution</t>
+  </si>
+  <si>
+    <t>https://main--demoenvironment--lmanning2.aem.live/addc/en-us/residential/help-and-support/transfer-and-removal-of-electricity-services</t>
   </si>
   <si>
     <t>nileair-holidays.report.json</t>
@@ -109,6 +112,24 @@
     <t>https://www.nileair.com/travelling-pets</t>
   </si>
   <si>
+    <t>addc/en-us/residential/overview.report.json</t>
+  </si>
+  <si>
+    <t>["hero-residential","cards-usp-overlay","cards-usp-overlay","cards-news"]</t>
+  </si>
+  <si>
+    <t>addc/en-us/residential/overview</t>
+  </si>
+  <si>
+    <t>residential</t>
+  </si>
+  <si>
+    <t>2026-09-17T05:56:42.554Z</t>
+  </si>
+  <si>
+    <t>https://taqadistribution.com/addc/en-us/residential/overview</t>
+  </si>
+  <si>
     <t>addc/en-us/business/help-and-support/certificates.report.json</t>
   </si>
   <si>
@@ -118,28 +139,22 @@
     <t>addc/en-us/business/help-and-support/certificates</t>
   </si>
   <si>
-    <t>help-and-support</t>
-  </si>
-  <si>
     <t>2026-09-16T08:55:32.399Z</t>
   </si>
   <si>
-    <t>TAQA Distribution</t>
-  </si>
-  <si>
     <t>https://taqadistribution.com/addc/en-us/business/help-and-support/certificates</t>
   </si>
   <si>
     <t>addc/en-us/residential/help-and-support/transfer-and-removal-of-electricity-services.report.json</t>
   </si>
   <si>
+    <t>[]</t>
+  </si>
+  <si>
     <t>addc/en-us/residential/help-and-support/transfer-and-removal-of-electricity-services</t>
   </si>
   <si>
-    <t>2026-09-16T08:55:44.447Z</t>
-  </si>
-  <si>
-    <t>https://taqadistribution.com/addc/en-us/residential/help-and-support/transfer-and-removal-of-electricity-services</t>
+    <t>2026-09-21T07:34:45.422Z</t>
   </si>
 </sst>
 </file>
@@ -528,7 +543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="50" customWidth="1"/>
@@ -610,21 +625,21 @@
         <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -633,24 +648,24 @@
         <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G4" t="s">
         <v>14</v>
       </c>
       <c r="H4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
@@ -659,36 +674,36 @@
         <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G5" t="s">
         <v>14</v>
       </c>
       <c r="H5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G6" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="H6" t="s">
         <v>38</v>
@@ -699,25 +714,51 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="F7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G7" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="H7" t="s">
-        <v>42</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-help-and-support.report.xlsx
+++ b/tools/importer/reports/import-help-and-support.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="47">
   <si>
     <t>_reportFile</t>
   </si>
@@ -73,7 +73,7 @@
     <t>help-and-support</t>
   </si>
   <si>
-    <t>2026-09-21T10:07:19.295Z</t>
+    <t>2026-09-21T11:51:45.269Z</t>
   </si>
   <si>
     <t>TAQA Distribution</t>
@@ -148,13 +148,10 @@
     <t>addc/en-us/residential/help-and-support/transfer-and-removal-of-electricity-services.report.json</t>
   </si>
   <si>
-    <t>[]</t>
-  </si>
-  <si>
     <t>addc/en-us/residential/help-and-support/transfer-and-removal-of-electricity-services</t>
   </si>
   <si>
-    <t>2026-09-21T07:34:45.422Z</t>
+    <t>2026-09-21T11:52:02.921Z</t>
   </si>
 </sst>
 </file>
@@ -740,10 +737,10 @@
         <v>44</v>
       </c>
       <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
         <v>45</v>
-      </c>
-      <c r="C8" t="s">
-        <v>46</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
@@ -752,7 +749,7 @@
         <v>19</v>
       </c>
       <c r="F8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G8" t="s">
         <v>21</v>

--- a/tools/importer/reports/import-help-and-support.report.xlsx
+++ b/tools/importer/reports/import-help-and-support.report.xlsx
@@ -73,7 +73,7 @@
     <t>help-and-support</t>
   </si>
   <si>
-    <t>2026-09-21T11:51:45.269Z</t>
+    <t>2026-09-21T12:07:41.276Z</t>
   </si>
   <si>
     <t>TAQA Distribution</t>
@@ -151,7 +151,7 @@
     <t>addc/en-us/residential/help-and-support/transfer-and-removal-of-electricity-services</t>
   </si>
   <si>
-    <t>2026-09-21T11:52:02.921Z</t>
+    <t>2026-09-21T12:08:01.623Z</t>
   </si>
 </sst>
 </file>

--- a/tools/importer/reports/import-help-and-support.report.xlsx
+++ b/tools/importer/reports/import-help-and-support.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>_reportFile</t>
   </si>
@@ -19,12 +19,6 @@
     <t>blocks</t>
   </si>
   <si>
-    <t>error</t>
-  </si>
-  <si>
-    <t>errorStack</t>
-  </si>
-  <si>
     <t>path</t>
   </si>
   <si>
@@ -49,9 +43,6 @@
     <t>["hero-support","carousel-quicklink","columns-appbanner","carousel-tips","carousel-tips","accordion-faq","cards-support"]</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>index</t>
   </si>
   <si>
@@ -61,35 +52,13 @@
     <t>help-and-support</t>
   </si>
   <si>
-    <t>2026-09-22T09:05:27.409Z</t>
+    <t>2026-09-22T11:48:52.519Z</t>
   </si>
   <si>
     <t>TAQA Distribution</t>
   </si>
   <si>
     <t>https://taqadistribution.com/addc/en-us/residential/help-and-support/transfer-and-removal-of-electricity-services</t>
-  </si>
-  <si>
-    <t>addc/en-us/residential/help-and-support/transfer-and-removal-of-electricity-services.report.json</t>
-  </si>
-  <si>
-    <t>CustomImportScript.default not found after 10s. The bundled script may not have loaded correctly. Check browser console for errors.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Error: CustomImportScript.default not found after 10s. The bundled script may not have loaded correctly. Check browser console for errors.
-    at processUrl (file:///home/node/.excat-marketplaces/excat-marketplace/excat/skills/excat-content-import/scripts/run-bulk-import.js:662:13)
-    at runNextTicks (node:internal/process/task_queues:65:5)
-    at process.processImmediate (node:internal/timers:472:9)
-    at async main (file:///home/node/.excat-marketplaces/excat-marketplace/excat/skills/excat-content-import/scripts/run-bulk-import.js:954:22)</t>
-  </si>
-  <si>
-    <t>addc/en-us/residential/help-and-support/transfer-and-removal-of-electricity-services</t>
-  </si>
-  <si>
-    <t>failed</t>
-  </si>
-  <si>
-    <t>2026-09-22T09:00:19.198Z</t>
   </si>
 </sst>
 </file>
@@ -478,17 +447,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="5" width="50" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="26" customWidth="1"/>
-    <col min="9" max="9" width="19" customWidth="1"/>
-    <col min="10" max="10" width="50" customWidth="1"/>
+    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="2" max="2" width="50" customWidth="1"/>
+    <col min="3" max="3" width="7" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="26" customWidth="1"/>
+    <col min="7" max="7" width="19" customWidth="1"/>
+    <col min="8" max="8" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -513,79 +484,35 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="B2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>14</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>15</v>
-      </c>
-      <c r="H2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J3" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1"/>
+  <autoFilter ref="A1:H1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
